--- a/it_forms/012_it_support_authorization_form--it_forms.xlsx
+++ b/it_forms/012_it_support_authorization_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'IT'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'admin'}</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Admin'}</t>
+          <t>Admin</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'limited'}</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Limited'}</t>
+          <t>Limited</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'full'}</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Full'}</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'custom'}</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Custom'}</t>
+          <t>Custom</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Laptop'}</t>
+          <t>Laptop</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mobile_phone'}</t>
+          <t>mobile_phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mobile Phone'}</t>
+          <t>Mobile Phone</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'printer'}</t>
+          <t>printer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Printer'}</t>
+          <t>Printer</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'network_switch'}</t>
+          <t>network_switch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Network Switch'}</t>
+          <t>Network Switch</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'windows'}</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Windows'}</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'linux'}</t>
+          <t>linux</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Linux'}</t>
+          <t>Linux</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'mac'}</t>
+          <t>mac</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Mac'}</t>
+          <t>Mac</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'approve'}</t>
+          <t>approve</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Approve'}</t>
+          <t>Approve</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'deny'}</t>
+          <t>deny</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Deny'}</t>
+          <t>Deny</t>
         </is>
       </c>
     </row>
